--- a/output_boron/boron_Intermediate_foster_2012.xlsx
+++ b/output_boron/boron_Intermediate_foster_2012.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="264">
   <si>
     <t>NA</t>
   </si>
@@ -1370,7 +1370,7 @@
     <t xml:space="preserve">10.1016/j.epsl.2012.06.007</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.ncei.noaa.gov/pub/data/paleo/climate_forcing/trace_gases/Paleo-pCO2/boron_isotopes_foster_2012.xlsx</t>
+    <t xml:space="preserve">boron_isotopes_foster_2012_p1.0.xlsx</t>
   </si>
   <si>
     <t xml:space="preserve">Harper and Giulivi</t>
@@ -1389,9 +1389,6 @@
   </si>
   <si>
     <t xml:space="preserve">MC-ICPMS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Note that air-sea disequilibrium in this study was acknowledged but not subtracted.</t>
   </si>
   <si>
     <t xml:space="preserve">761_B_5_4_123_125</t>
@@ -1444,7 +1441,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1504,12 +1501,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <b/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <u val="single"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1623,7 +1614,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1705,7 +1696,6 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2312,7 +2302,7 @@
       <c r="B5" t="s">
         <v>241</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="C5" t="s">
         <v>242</v>
       </c>
       <c r="D5" t="s">
@@ -2378,18 +2368,18 @@
       <c r="X5" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y5" t="s">
-        <v>249</v>
+      <c r="Y5" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="6" ht="19" customHeight="1">
       <c r="A6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B6" t="s">
         <v>241</v>
       </c>
-      <c r="C6" s="29" t="s">
+      <c r="C6" t="s">
         <v>242</v>
       </c>
       <c r="D6" t="s">
@@ -2455,18 +2445,18 @@
       <c r="X6" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y6" t="s">
-        <v>249</v>
+      <c r="Y6" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="7" ht="19" customHeight="1">
       <c r="A7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B7" t="s">
         <v>241</v>
       </c>
-      <c r="C7" s="29" t="s">
+      <c r="C7" t="s">
         <v>242</v>
       </c>
       <c r="D7" t="s">
@@ -2532,18 +2522,18 @@
       <c r="X7" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y7" t="s">
-        <v>249</v>
+      <c r="Y7" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1">
       <c r="A8" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B8" t="s">
         <v>241</v>
       </c>
-      <c r="C8" s="29" t="s">
+      <c r="C8" t="s">
         <v>242</v>
       </c>
       <c r="D8" t="s">
@@ -2609,18 +2599,18 @@
       <c r="X8" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y8" t="s">
-        <v>249</v>
+      <c r="Y8" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1">
       <c r="A9" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B9" t="s">
         <v>241</v>
       </c>
-      <c r="C9" s="29" t="s">
+      <c r="C9" t="s">
         <v>242</v>
       </c>
       <c r="D9" t="s">
@@ -2686,18 +2676,18 @@
       <c r="X9" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y9" t="s">
-        <v>249</v>
+      <c r="Y9" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1">
       <c r="A10" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B10" t="s">
         <v>241</v>
       </c>
-      <c r="C10" s="29" t="s">
+      <c r="C10" t="s">
         <v>242</v>
       </c>
       <c r="D10" t="s">
@@ -2763,18 +2753,18 @@
       <c r="X10" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y10" t="s">
-        <v>249</v>
+      <c r="Y10" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1">
       <c r="A11" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B11" t="s">
         <v>241</v>
       </c>
-      <c r="C11" s="29" t="s">
+      <c r="C11" t="s">
         <v>242</v>
       </c>
       <c r="D11" t="s">
@@ -2840,18 +2830,18 @@
       <c r="X11" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y11" t="s">
-        <v>249</v>
+      <c r="Y11" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1">
       <c r="A12" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B12" t="s">
         <v>241</v>
       </c>
-      <c r="C12" s="29" t="s">
+      <c r="C12" t="s">
         <v>242</v>
       </c>
       <c r="D12" t="s">
@@ -2917,18 +2907,18 @@
       <c r="X12" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y12" t="s">
-        <v>249</v>
+      <c r="Y12" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1">
       <c r="A13" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B13" t="s">
         <v>241</v>
       </c>
-      <c r="C13" s="29" t="s">
+      <c r="C13" t="s">
         <v>242</v>
       </c>
       <c r="D13" t="s">
@@ -2994,18 +2984,18 @@
       <c r="X13" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y13" t="s">
-        <v>249</v>
+      <c r="Y13" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1">
       <c r="A14" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B14" t="s">
         <v>241</v>
       </c>
-      <c r="C14" s="29" t="s">
+      <c r="C14" t="s">
         <v>242</v>
       </c>
       <c r="D14" t="s">
@@ -3071,18 +3061,18 @@
       <c r="X14" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y14" t="s">
-        <v>249</v>
+      <c r="Y14" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1">
       <c r="A15" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B15" t="s">
         <v>241</v>
       </c>
-      <c r="C15" s="29" t="s">
+      <c r="C15" t="s">
         <v>242</v>
       </c>
       <c r="D15" t="s">
@@ -3148,18 +3138,18 @@
       <c r="X15" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y15" t="s">
-        <v>249</v>
+      <c r="Y15" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1">
       <c r="A16" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B16" t="s">
         <v>241</v>
       </c>
-      <c r="C16" s="29" t="s">
+      <c r="C16" t="s">
         <v>242</v>
       </c>
       <c r="D16" t="s">
@@ -3225,18 +3215,18 @@
       <c r="X16" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y16" t="s">
-        <v>249</v>
+      <c r="Y16" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1">
       <c r="A17" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B17" t="s">
         <v>241</v>
       </c>
-      <c r="C17" s="29" t="s">
+      <c r="C17" t="s">
         <v>242</v>
       </c>
       <c r="D17" t="s">
@@ -3302,18 +3292,18 @@
       <c r="X17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y17" t="s">
-        <v>249</v>
+      <c r="Y17" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1">
       <c r="A18" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B18" t="s">
         <v>241</v>
       </c>
-      <c r="C18" s="29" t="s">
+      <c r="C18" t="s">
         <v>242</v>
       </c>
       <c r="D18" t="s">
@@ -3379,18 +3369,18 @@
       <c r="X18" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y18" t="s">
-        <v>249</v>
+      <c r="Y18" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1">
       <c r="A19" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B19" t="s">
         <v>241</v>
       </c>
-      <c r="C19" s="29" t="s">
+      <c r="C19" t="s">
         <v>242</v>
       </c>
       <c r="D19" t="s">
@@ -3456,18 +3446,18 @@
       <c r="X19" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y19" t="s">
-        <v>249</v>
+      <c r="Y19" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1">
       <c r="A20" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B20" t="s">
         <v>241</v>
       </c>
-      <c r="C20" s="29" t="s">
+      <c r="C20" t="s">
         <v>242</v>
       </c>
       <c r="D20" t="s">
@@ -3533,8 +3523,8 @@
       <c r="X20" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y20" t="s">
-        <v>249</v>
+      <c r="Y20" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1">
@@ -3801,24 +3791,6 @@
       <formula>#REF!="no"</formula>
     </cfRule>
   </conditionalFormatting>
-  <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1h"/>
-    <hyperlink ref="C6" r:id="rId2h"/>
-    <hyperlink ref="C7" r:id="rId3h"/>
-    <hyperlink ref="C8" r:id="rId4h"/>
-    <hyperlink ref="C9" r:id="rId5h"/>
-    <hyperlink ref="C10" r:id="rId6h"/>
-    <hyperlink ref="C11" r:id="rId7h"/>
-    <hyperlink ref="C12" r:id="rId8h"/>
-    <hyperlink ref="C13" r:id="rId9h"/>
-    <hyperlink ref="C14" r:id="rId10h"/>
-    <hyperlink ref="C15" r:id="rId11h"/>
-    <hyperlink ref="C16" r:id="rId12h"/>
-    <hyperlink ref="C17" r:id="rId13h"/>
-    <hyperlink ref="C18" r:id="rId14h"/>
-    <hyperlink ref="C19" r:id="rId15h"/>
-    <hyperlink ref="C20" r:id="rId16h"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <extLst>
